--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -649,7 +649,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Với mỗi item, hỏi nếu xóa nó thì verdict hoặc boundary có thể đổi không.</t>
+          <t>Thông tin cần giữ trong packet quyết định hoàn tiền booking B17: Chính sách hủy 48h đúng phiên bản (a), Thời gian check-in còn 36h (b), và Điều khoản non-refundable riêng của booking B17 nếu có (e). Sở thích phòng (c) và lịch sử chuyến đi cũ (d) không ảnh hưởng đến điều kiện hoàn tiền.</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét tác động mạnh nhất có thể xảy ra khi gọi tool hợp lệ.</t>
+          <t>Tool `get_or_create_profile(email)` có nhánh tạo mới làm thay đổi trạng thái trong cơ sở dữ liệu nếu hồ sơ chưa tồn tại, do đó phải được phân loại vào nhóm hành động/ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thông tin định danh do người dùng cung cấp khỏi bằng chứng thay đổi theo thời gian cần truy xuất.</t>
+          <t>Người dùng đã cung cấp đủ mã chuyến bay và ngày bay, và câu trả lời bắt buộc phải dựa trên dữ liệu mới nhất từ công cụ; chính sách tool-choice đúng là bắt buộc dùng `flight_status` (forced tool-choice).</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng dựa vào động từ HTTP hay tên hàm; hãy đọc tác động được mô tả.</t>
+          <t>Các lời gọi làm thay đổi trạng thái bên ngoài (state-modifying): `GET /report?mark_seen=true` thay đổi trạng thái đã xem trên server (a), `send_email` gửi email thật ra ngoài (d), và `reserve_room(hold=true)` tạo bản ghi giữ phòng tạm (e). `search_docs` và `preview_email` là thao tác chỉ đọc/cục bộ.</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy xét cả các đối số mặc định trước khi phân loại.</t>
+          <t>Hàm `check_coupon(code, apply=True)` có đối số mặc định `apply=True` làm thay đổi giỏ hàng phía máy chủ, nên lời gọi này là một hành động ghi dữ liệu (write action).</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt không nhận được phản hồi với việc không có tác động nào xảy ra.</t>
+          <t>Khi `charge_card` bị timeout, cổng thanh toán có thể đã trừ tiền. Nếu client tạo request ID mới để thử lại thì có nguy cơ trừ tiền hai lần; cách sửa đúng là đối soát giao dịch và dùng lại đúng idempotency key ban đầu.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_02_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_02_22_Cau.xlsx
@@ -682,10 +682,26 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không dùng nhãn “liên quan” chung chung; hãy nói nó làm đổi nhánh nào.
-Phân tích theo nguyên lý thiết kế: Không dùng nhãn “liên quan” chung chung; hãy nói nó làm đổi nhánh nào.</t>
+- 1.0 điểm: Giải thích nhóm Giữ bằng tác động rẽ nhánh cụ thể (ngưỡng 5tr -&gt; biên nhận 5.4tr vượt ngưỡng -&gt; chữ ký ngoại lệ chuyển nhánh sang Approve).
+- 1.0 điểm: Giải thích nhóm Loại thông qua chứng minh không làm thay đổi bất kỳ nhánh logic nào của quyết định.
+- 1.0 điểm: Chỉ ra chính xác các thông tin cần kiểm tra độ mới (hiệu lực chính sách chi tiêu và hiệu lực ủy quyền của quản lý).
+- 1.0 điểm: Trình bày chặt chẽ theo nguyên tắc Context Minimization &amp; Security Compliance.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Giải thích từng nhóm Giữ / Loại dựa trên tác động lên quyết định rẽ nhánh logic:
+- Nhóm GIỮ:
+  + Hạn mức chính sách 5 triệu: Thiết lập ngưỡng cơ sở (Baseline threshold). Đây là điều kiện phân nhánh chính: nếu chi tiêu &lt;= 5 triệu thì duyệt tự động; nếu &gt; 5 triệu thì bắt buộc chuyển sang nhánh phê duyệt ngoại lệ.
+  + Biên nhận 5,4 triệu: Dữ liệu thực tế phát sinh. Khoản chi 5,4 triệu vượt ngưỡng 5 triệu (+400.000 VNĐ), trực tiếp kích hoạt rẽ nhánh sang yêu cầu ngoại lệ thay vì từ chối thẳng.
+  + Phê duyệt ngoại lệ của quản lý đã ký: Thẩm quyền giải quyết ngoại lệ. Khi có văn bản này, nhánh quyết định chuyển từ 'Reject (do vượt hạn mức)' sang 'Approve (được miễn trừ hợp lệ)'.
+- Nhóm LOẠI:
+  + Tiểu sử nhân viên, thực đơn văn phòng, gợi ý du lịch: Dữ liệu rác/nhiễu. Chúng không tham gia vào bất kỳ mệnh đề điều kiện nào trong quy tắc phê duyệt tài chính, hoàn toàn không làm đổi nhánh quyết định, gây lãng phí token và nguy cơ hallucination.
+  + Ba biên nhận năm ngoái: Thuộc kỳ kế toán đã đóng và giao dịch khác, không có giá trị đối chiếu pháp lý cho chứng từ phát sinh hiện tại.
+2. Thông tin bắt buộc cần kiểm tra độ mới (Freshness Verification):
+- Bản quy định 'Hạn mức chính sách 5 triệu': Cần kiểm tra phiên bản chính sách có đang có hiệu lực tại ngày lập biên nhận hay không (tránh dùng chính sách cũ đã bị thay thế).
+- 'Phê duyệt ngoại lệ của quản lý': Cần kiểm tra thẩm quyền của người ký tại thời điểm ký (quản lý còn đương nhiệm và có hạn mức phê duyệt tới 5,4 triệu hay không).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Context Relevance Selection trong thiết kế AI System đòi hỏi mọi phần tử ngữ cảnh đưa vào Prompt phải có tác động định hướng trực tiếp tới nhánh quyết định logic (Decision Branching). Những thông tin không làm thay đổi hàm mục tiêu cần phải bị thanh lọc để bảo vệ không gian ngữ cảnh và đảm bảo các quyết định tài chính luôn dựa trên dữ liệu có hiệu lực thời gian thực.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Context Window Management Guidelines &amp; Enterprise Architecture Patterns for Decision Support Systems (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering)</t>
         </is>
       </c>
     </row>
@@ -781,10 +797,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh lịch sử gốc với phần tóm tắt theo từng loại thông tin bắt buộc, không theo số token.
-Phân tích theo nguyên lý thiết kế: So sánh lịch sử gốc với phần tóm tắt theo từng loại thông tin bắt buộc, không theo số token.</t>
+- 1.0 điểm: Tạo bản tóm tắt nén chính xác, giữ nguyên các lựa chọn cập nhật mới nhất (macOS, &lt;=30tr, chưa mua).
+- 1.0 điểm: Xử lý đúng đắn mối quan hệ giữa Nguồn A và Nguồn B dựa trên độ tươi mới và thời hạn hiệu lực.
+- 1.0 điểm: Giữ lại khoảng trống thông tin về GPU và lọc bỏ hoàn toàn các lượt chào hỏi xã giao.
+- 1.0 điểm: Xây dựng checklist đối chiếu theo từng loại thông tin bắt buộc để chứng minh tính đầy đủ của bản nén.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Trạng thái tóm tắt nén từ lịch sử (Compacted State):
+- Mục tiêu &amp; Ngân sách: Khảo sát danh sách lựa chọn laptop macOS với ngân sách tối đa 30 triệu VNĐ (ghi nhận: đã hủy bỏ lựa chọn Windows ban đầu).
+- Trạng thái quyết định: Đang trong giai đoạn lập danh sách cân nhắc, chưa tiến hành mua hàng.
+- Dữ liệu thị trường hợp lệ: Nguồn B (giá 29 triệu VNĐ, thu thập cách đây 10 phút, còn hiệu lực 20 phút) là nguồn dữ liệu giá có độ tươi mới cao và đáng tin cậy nhất hiện tại. Nguồn A (giá 28 triệu VNĐ, thu thập cách đây 3 ngày, không rõ thời hạn) được lưu vết để đối chiếu lịch sử nhưng đánh dấu là dữ liệu cũ cần xác minh lại.
+- Khoảng trống thông tin (Information Gaps): Chưa xác định người dùng có yêu cầu đồ họa/GPU chuyên dụng hay không.
+- Dữ liệu loại bỏ hoàn toàn: 8 lượt chào hỏi xã giao (chitchat filtering).
+2. Checklist đối chiếu chứng minh phần tóm tắt đã đầy đủ:
+- [ ] Ràng buộc cứng (Hard Constraints): Đã giữ ngân sách &lt;= 30 triệu và hệ điều hành cuối cùng là macOS (loại Windows)?
+- [ ] Giai đoạn giao dịch (Intent Stage): Đã phản ánh chính xác trạng thái 'chỉ lập danh sách, chưa mua'?
+- [ ] Nguồn gốc &amp; Độ mới dữ liệu (Data Provenance &amp; Freshness): Đã ưu tiên giá Nguồn B (29tr, còn hạn 20p) và ghi chú rủi ro độ trễ của Nguồn A (28tr, 3 ngày)?
+- [ ] Khoảng trống thông tin cần khai thác (Open Gaps): Đã ghi nhận rõ câu hỏi còn thiếu về nhu cầu GPU để làm rõ ở lượt tiếp theo?
+- [ ] Khử nhiễu hội thoại (Noise Reduction): Đã thanh lọc 100% các lượt chào hỏi vô thưởng vô phạt không mang giá trị ngữ nghĩa?
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật History Compaction (nén lịch sử hội thoại) nhằm mục tiêu giảm thiểu kích thước context window mà không làm thất thoát các trạng thái ràng buộc cốt lõi. Một checklist đối chiếu dựa trên các loại thông tin bắt buộc (ràng buộc cứng, ý định, độ tươi dữ liệu, khoảng trống cần hỏi) giúp kiểm toán được tính toàn vẹn của trạng thái nén, độc lập hoàn toàn với số lượng token hiển thị.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation - Memory &amp; Conversation Summary Buffer (https://python.langchain.com/docs/concepts/)</t>
         </is>
       </c>
     </row>
@@ -969,10 +1002,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt việc đọc dữ liệu, xử lý cục bộ và thay đổi dữ liệu bên ngoài.
-Phân tích theo nguyên lý thiết kế: Phân biệt việc đọc dữ liệu, xử lý cục bộ và thay đổi dữ liệu bên ngoài.</t>
+- 1.0 điểm: Xác định đúng bộ công cụ tối ưu không chồng lấn được giữ lại (`query_sales` và `make_chart`).
+- 1.0 điểm: Phân tích và loại bỏ `query_orders` do nguy cơ chồng lấn công năng gây nhiễu cho router.
+- 1.0 điểm: Giải thích rõ việc loại bỏ `edit_invoice` và `send_report` do vi phạm quy tắc 'chỉ đọc' và 'cục bộ'.
+- 1.0 điểm: Chỉ ra lỗ hổng bảo mật nghiêm trọng của `sql_any` (vi phạm Least Privilege, nguy cơ SQL injection).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bộ tool tối ưu không chồng chéo được GIỮ:
+- `query_sales`: Công cụ đọc dữ liệu doanh số tổng hợp.
+- `make_chart`: Công cụ tính toán cục bộ để vẽ biểu đồ từ dữ liệu đã truy vấn.
+2. Giải thích lý do Giữ hoặc Loại từng công cụ:
+- `query_sales`: GIỮ. Đây là công cụ đọc (read-only) phục vụ trực tiếp vai trò phân tích doanh thu của agent.
+- `make_chart`: GIỮ. Đây là công cụ xử lý cục bộ (local transformation / visual rendering), không tạo side-effect ra hệ thống bên ngoài, đáp ứng đúng yêu cầu 'tạo biểu đồ cục bộ'.
+- `query_orders`: LOẠI (hoặc tích hợp vào query_sales). Để ngăn chặn tình trạng chồng chéo tính năng (tool overlap). Khi có cả hai tool đọc cùng miền dữ liệu bán hàng, LLM thường bối rối trong việc lựa chọn tool, làm giảm độ tin cậy của router.
+- `edit_invoice`: LOẠI BỎ TRIỆT ĐỂ. Vi phạm nguyên tắc phân quyền và ranh giới vai trò. Agent có vai trò 'chỉ đọc dữ liệu', trong khi `edit_invoice` là hành động ghi (mutation/write) làm thay đổi dữ liệu hóa đơn, tiềm ẩn rủi ro phá hủy tính toàn vẹn tài chính.
+- `send_report`: LOẠI BỎ. Vi phạm ranh giới vai trò. Gửi báo cáo ra ngoài qua email/slack là hành vi tác động ngoại vi (side-effect), vượt quá quyền hạn phân tích cục bộ.
+- `sql_any`: LOẠI BỎ TRIỆT ĐỂ. Vi phạm nghiêm trọng nguyên tắc đặc quyền tối thiểu (Least Privilege) và an toàn hệ thống. Công cụ cho phép chạy SQL tùy ý tạo nguy cơ SQL Injection, rò rỉ dữ liệu nhạy cảm hoặc drop bảng ngoài ý muốn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ranh giới danh mục công cụ (Tool Inventory Boundary) yêu cầu tách bạch tuyệt đối giữa ba nhóm: truy vấn chỉ đọc (read-only queries), xử lý cục bộ (local computation) và đột biến trạng thái ngoại vi (external side-effects). Việc giới hạn công cụ ở mức tối thiểu, không chồng lấn giúp loại trừ nguy cơ Excessive Agency (OWASP LLM08) và đảm bảo router hoạt động xác định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Function Calling Best Practices &amp; OWASP Top 10 for Large Language Models - LLM08: Excessive Agency (https://platform.openai.com/docs/guides/function-calling)</t>
         </is>
       </c>
     </row>
@@ -1060,10 +1108,20 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt tool agent có thể dùng với tool mà lượt hiện tại thực sự cần.
-Phân tích theo nguyên lý thiết kế: Phân biệt tool agent có thể dùng với tool mà lượt hiện tại thực sự cần.</t>
+- 1.0 điểm: Lập danh sách công cụ chính xác cho lượt hiện tại (`spellcheck`, hoặc kèm `read_doc`), loại bỏ các tool có side-effect.
+- 1.0 điểm: Nêu rõ điều kiện xác nhận rõ ràng của người dùng để kích hoạt `edit_doc`.
+- 1.0 điểm: Nêu rõ điều kiện phê duyệt bản nháp cuối cùng để kích hoạt `send_email` (Human-in-the-loop).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Danh sách công cụ phơi bày ở lượt hiện tại (Least Privilege Tool Exposure):
+- Danh sách công cụ cho lượt này: `[spellcheck]` (hoặc `[read_doc, spellcheck]` nếu nội dung văn bản chưa có sẵn trong context hội thoại; nếu văn bản đã ở trong context, chỉ phơi bày duy nhất `spellcheck`).
+- Tạm thời ẩn hoàn toàn: `edit_doc` và `send_email`.
+2. Điều kiện kích hoạt bổ sung các công cụ có quyền hạn cao:
+- Khi nào thêm `edit_doc`: Chỉ đưa vào danh sách công cụ khả dụng khi người dùng đã xem xong danh sách lỗi chính tả được phát hiện và đưa ra yêu cầu/xác nhận rõ ràng: 'Hãy chỉnh sửa các lỗi này vào tài liệu' hoặc bấm nút 'Áp dụng sửa lỗi'.
+- Khi nào thêm `send_email`: Chỉ cấp quyền truy cập công cụ này khi tài liệu đã được chỉnh sửa hoàn tất, người dùng đã duyệt bản xem trước (preview) cuối cùng và đưa ra lệnh gửi dứt khoát kèm xác nhận người nhận và tiêu đề email.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Least Privilege Tool Exposure (phơi bày công cụ theo đặc quyền tối thiểu theo từng lượt) đòi hỏi hệ thống chỉ cung cấp những công cụ thực sự cần thiết cho yêu cầu cụ thể của lượt tương tác hiện tại. Việc giấu các công cụ có side-effect ghi/gửi (`edit_doc`, `send_email`) khi người dùng chỉ yêu cầu 'kiểm tra' giúp ngăn chặn hoàn toàn nguy cơ mô hình tự ý thực thi hành động vượt quyền trước khi có sự đồng ý của con người.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Tool Use Documentation &amp; OWASP Top 10 for LLM: LLM08 Excessive Agency (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering)</t>
         </is>
       </c>
     </row>
@@ -1247,10 +1305,39 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Hai con số có cùng cấu trúc nhưng khác thông tin về nguồn gốc.
-Phân tích theo nguyên lý thiết kế: Hai con số có cùng cấu trúc nhưng khác thông tin về nguồn gốc.</t>
+- 1.0 điểm: Chuẩn hóa dữ liệu thành cấu trúc rõ ràng phản ánh đầy đủ metadata nguồn gốc (nguồn, thời điểm, khu vực, trạng thái).
+- 1.0 điểm: Đưa ra quyết định chọn kết quả A kèm lý giải xác đáng về tính minh bạch của nguồn gốc.
+- 1.0 điểm: Đề xuất phương án xử lý kết quả B chuẩn xác (loại bỏ khỏi context, cách ly, kích hoạt refresh cache).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chuẩn hóa cấu trúc bản ghi nguồn gốc dữ liệu (Data Provenance Schema):
+```json
+{
+  "record_A": {
+    "sku": "SKU-X",
+    "region": "VN",
+    "price": 120,
+    "source_system": "API_P",
+    "fetched_at": "2026-10-23T10:00:00Z",
+    "provenance_status": "VERIFIED_ACTIVE"
+  },
+  "record_B": {
+    "sku": "X",
+    "region": "UNKNOWN",
+    "price": 100,
+    "source_system": "UNVERIFIED_CACHE",
+    "fetched_at": null,
+    "provenance_status": "UNTRUSTED_STALE"
+  }
+}
+```
+2. Quyết định: CHỈ SỬ DỤNG KẾT QUẢ A cho các quyết định nghiệp vụ hiện tại.
+3. Giải thích cách xử lý kết quả B:
+- Đánh dấu vô hiệu hóa (Invalidate &amp; Quarantine): Kết quả B thiếu hoàn toàn metadata nguồn gốc (không rõ API nguồn, không có timestamp, phạm vi vùng địa lý mập mờ). Mức giá 100 có thể là giá cũ, giá ở thị trường quốc tế hoặc dữ liệu rác từ phiên kiểm thử trước.
+- Xử lý kỹ thuật: Không nạp kết quả B vào ngữ cảnh của mô hình. Ghi log cảnh báo về việc bộ nhớ đệm chứa dữ liệu thiếu metadata nguồn gốc và kích hoạt tiến trình làm mới bộ nhớ đệm (cache purge / refresh) từ API chính thống P.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Provenance Labeling (gắn nhãn nguồn gốc dữ liệu) là nền tảng để đánh giá tính xác thực của thông tin đầu vào. Hai con số có thể giống hệt về mặt cấu trúc (ví dụ: trường price), nhưng con số thiếu thông tin về nguồn cấp, thời điểm lấy và phạm vi địa lý phải bị coi là không đáng tin cậy (untrusted) để bảo vệ hệ thống khỏi các quyết định sai lệch nghiêm trọng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C PROV-DM: The PROV Data Model (https://www.w3.org/TR/prov-dm/) &amp; Data Lineage Best Practices</t>
         </is>
       </c>
     </row>
@@ -1337,10 +1424,36 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ quyết định tiếp theo, không bắt đầu từ toàn bộ dữ liệu trả về.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ quyết định tiếp theo, không bắt đầu từ toàn bộ dữ liệu trả về.</t>
+- 1.0 điểm: Thiết kế cấu trúc JSON/Dictionary tối thiểu gồm các trường thiết yếu (`doc_id`, `title`, `published_at`, `snippet`, `url`).
+- 1.0 điểm: Giải thích thuyết phục việc giữ lại các trường phục vụ quyết định (ngày xuất bản để so sánh độ mới, snippet để kiểm tra tính liên quan).
+- 1.0 điểm: Giải thích rõ lý do loại bỏ các trường rác và nguy cơ bảo mật (`raw_html`, `cookie`, `tracking_code`).
+- 1.0 điểm: Đề xuất phương án tiền xử lý (pre-filter/sort) ở tầng ứng dụng thay vì đưa cả 100 tài liệu vào context.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế mục ngữ cảnh tối thiểu (Minimal Context Item):
+```json
+{
+  "doc_id": "doc_042",
+  "title": "Chính sách bảo mật dữ liệu năm 2026",
+  "published_at": "2026-08-15T09:00:00Z",
+  "snippet": "Cập nhật các quy định mới về lưu trữ và bảo vệ dữ liệu khách hàng theo tiêu chuẩn mới...",
+  "url": "https://example.com/policies/data-privacy-2026"
+}
+```
+2. Giải thích các trường GIỮ và BỎ:
+- Các trường GIỮ:
+  + `doc_id` &amp; `url`: Định danh duy nhất và đường dẫn tài liệu phục vụ việc truy xuất nội dung chi tiết ở bước tiếp theo.
+  + `title` &amp; `snippet`: Đủ để mô hình đánh giá xem tài liệu có đúng là 'chính sách' liên quan hay không.
+  + `published_at`: Trường bắt buộc để so sánh thời gian và xếp hạng lọc ra 3 tài liệu mới nhất.
+- Các trường BỎ:
+  + `raw_html`: Lãng phí hàng nghìn token không cần thiết, làm loãng ngữ cảnh và tăng chi phí suy luận.
+  + `cookie`: Thông tin phiên duyệt web nhạy cảm, vi phạm bảo mật nếu đưa vào prompt của LLM.
+  + `tracking_code`: Mã đo lường vô nghĩa đối với nhiệm vụ trích xuất tri thức.
+3. Tối ưu hóa tầng ứng dụng trước khi nạp vào Prompt:
+Thay vì nạp toàn bộ 100 mục vào prompt để model tự lọc, hệ thống cần sắp xếp (sort) theo `published_at` giảm dần và lọc trước ở tầng mã nguồn ứng dụng, chỉ đưa vào context 5–10 ứng viên chính sách tiềm năng nhất để model lựa chọn 3 tài liệu cuối cùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Context Minimization yêu cầu chỉ truyền những thuộc tính phục vụ trực tiếp cho quyết định tiếp theo. Đối với bài toán xếp hạng độ mới và chọn tài liệu, việc loại bỏ HTML thô, mã tracking và cookies giúp giảm tới 95% số lượng token, ngăn ngừa hiện tượng 'Lost in the Middle' và triệt tiêu nguy cơ rò rỉ thông tin nhạy cảm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Context Window Management Guidelines &amp; Precision Context Retrieval Techniques (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering)</t>
         </is>
       </c>
     </row>
@@ -1522,10 +1635,30 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Biện pháp kiểm soát phải gắn đúng với tác động, số tiền và đối tượng.
-Phân tích theo nguyên lý thiết kế: Biện pháp kiểm soát phải gắn đúng với tác động, số tiền và đối tượng.</t>
+- 1.0 điểm: Gán đúng mức rủi ro: A là Thấp (Low), B là Cao (High/Critical).
+- 1.0 điểm: Đưa ra bằng chứng thuyết phục dựa trên tính chất tự hủy của A và tác động tài chính thực (8 triệu) của B.
+- 1.0 điểm: Đề xuất kiểm soát tối thiểu cho A (audit log, rate limit).
+- 1.0 điểm: Đề xuất kiểm soát chặt chẽ cho B (Human-in-the-loop, xác nhận OTP, Idempotency key, bảo mật PCI-DSS).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân cấp mức rủi ro và bằng chứng hỗ trợ:
+- Lời gọi A (`hold(room, 10min)`):
+  + Mức rủi ro: THẤP (Low Risk).
+  + Bằng chứng: Hành động mang tính tạm thời, tự động hết hạn sau 10 phút, không trừ tiền thẻ tín dụng của khách, trạng thái có thể tự phục hồi/đảo ngược mà không để lại tổn thất tài chính hay pháp lý.
+- Lời gọi B (`confirm(room, card, 8_000_000)`):
+  + Mức rủi ro: CAO / NGHIÊM TRỌNG (High / Critical Risk).
+  + Bằng chứng: Trực tiếp trừ số tiền lớn (8.000.000 VNĐ) từ tài khoản thanh toán của người dùng, xác lập hợp đồng dịch vụ không thể tự ý hủy nếu không mất phí, phát sinh hóa đơn tài chính và gửi xác nhận pháp lý chính thức.
+2. Biện pháp kiểm soát tối thiểu bắt buộc:
+- Kiểm soát cho Lời gọi A:
+  + Ghi log kiểm toán (Audit Logging) với session ID.
+  + Giới hạn tần suất gọi (Rate Limiting) để tránh việc người dùng hoặc bot lạm dụng giữ phòng ảo liên tục làm cạn kiệt phòng của khách sạn.
+- Kiểm soát cho Lời gọi B:
+  + Xác nhận chủ động từ con người (Human-in-the-loop / Explicit User Confirmation): Bắt buộc hiển thị modal tóm tắt giao dịch (tên khách sạn, số tiền 8 triệu, chính sách hủy) và yêu cầu người dùng xác nhận chủ động (nhập mã OTP hoặc xác thực vân tay/mật khẩu).
+  + Cơ chế chống lặp thanh toán (Idempotency Key): Gắn khóa duy nhất cho giao dịch thanh toán để ngăn việc trừ tiền 2 lần khi mạng chập chờn hoặc retry.
+  + Mã hóa và phân quyền thẻ (PCI-DSS tokenization): Không truyền thông tin thẻ trần qua LLM prompt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Action Risk Tiering (phân tầng rủi ro hành động) phân loại các công cụ dựa trên khả năng đảo ngược (reversibility) và tác động tài chính/pháp lý. Các hành động rủi ro cao như trừ tiền không bao giờ được phép thực thi tự động hoàn toàn (full autonomy) bởi LLM mà bắt buộc phải có cổng kiểm soát Human-in-the-loop và các rào chắn kỹ thuật thanh toán nghiêm ngặt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 for LLM - LLM08: Excessive Agency &amp; NIST AI Risk Management Framework (AI RMF) (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
@@ -1606,10 +1739,28 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Idempotency cần cả danh tính request lẫn bản ghi về kết quả.
-Phân tích theo nguyên lý thiết kế: Idempotency cần cả danh tính request lẫn bản ghi về kết quả.</t>
+- 1.0 điểm: Định nghĩa chính xác cấu trúc Idempotency Key dựa trên định danh học viên và khóa học.
+- 1.0 điểm: Mô tả đầy đủ các trạng thái và chuyển trạng thái (INITIATED -&gt; PROCESSING -&gt; COMPLETED/FAILED).
+- 1.0 điểm: Nêu rõ cơ chế khóa phân tán (Distributed Lock) ngăn chặn race conditions giữa các workers.
+- 1.0 điểm: Quy định rõ ràng hành vi khi replay: trả về kết quả đã hoàn thành trước đó kèm cờ replay mà không thực thi lại side-effect.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Danh tính Request (Idempotency Key):
+- Khóa định danh duy nhất được cấu tạo dạng: `idempotency_key = sha256(f"{student_id}:{course_id}:{issuance_epoch_cycle}")`.
+- Khóa này được sinh ngay từ khi sự kiện hoàn thành khóa học được kích hoạt và truyền kèm qua mọi lần retry của worker.
+2. Máy trạng thái và Các chuyển trạng thái (State Transitions):
+- Bảng lưu trữ `certificate_issuances` với khóa chính `idempotency_key`:
+  + `INITIATED`: Bản ghi được tạo khi worker bắt đầu nhận job.
+  + `PROCESSING`: Khóa phân tán (Distributed Lock, ví dụ qua Redis) được kích hoạt để đảm bảo tại một thời điểm chỉ có 1 worker duy nhất thực thi tiến trình cấp chứng chỉ.
+  + `COMPLETED`: Chứng chỉ đã tạo thành công, PDF đã upload lên Cloud Storage, email thông báo đã gửi, lưu trường `certificate_url` và `issued_at`.
+  + `FAILED`: Xử lý gặp sự cố kỹ thuật không thể khôi phục, giải phóng lock và ghi nhận lý do lỗi.
+3. Trạng thái và kết quả trả cho bên gọi khi có Replay (Xử lý lại job):
+- Nếu worker kiểm tra thấy `idempotency_key` đã ở trạng thái `COMPLETED`:
+  + Worker KHÔNG tạo lại PDF mới, KHÔNG gọi lại API gửi email để tránh spam học viên.
+  + Trả về ngay payload kết quả đã lưu trữ từ trước: `{'status': 'ALREADY_ISSUED', 'is_replay': True, 'certificate_id': 'CERT-789', 'certificate_url': 'https://...', 'issued_at': '...'}` với mã phản hồi thành công (HTTP 200/ACK).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Write Replay Safeguards trong kiến trúc phân tán dựa trên Idempotency Key để đảm bảo rằng việc thực thi lại nhiều lần một tác vụ ghi (mutation) vẫn đem lại kết quả nhất quán như thực thi một lần duy nhất. Điều này bảo vệ người dùng khỏi các hệ quả tiêu cực như nhận nhiều email chứng chỉ hoặc trùng lặp bản ghi dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler - Enterprise Integration Patterns: Idempotent Receiver &amp; Stripe API Idempotency Technical Documentation (https://martinfowler.com/articles/)</t>
         </is>
       </c>
     </row>
